--- a/cashflows_ON_USD_ley_ARG_NY_universo_solo_USD_2.xlsx
+++ b/cashflows_ON_USD_ley_ARG_NY_universo_solo_USD_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/mreverter_balanz_com/Documents/Escritorio/Info Solicitada/Cashflows net v2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/mreverter_balanz_com/Documents/Escritorio/Info Solicitada/Cashflows net v2 - TEST LOCAL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_56DB888BAD2EA0C966F93D7708BFF57760A3A3CB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C07927B4-78BE-4D17-BD82-36E0D9F283F7}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_56DB888BAD2EA0C966F93D7708BFF57760A3A3CB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C5B73E-28F7-4280-8C13-5DB97C497673}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflows" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Exacto público: flujo extraído de tabla pública accesible. Modelo desde PDF: construido con reglas indicadas en la hoja Metodologia.</t>
         </r>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8949" uniqueCount="1862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8957" uniqueCount="1864">
   <si>
     <t>Ticker</t>
   </si>
@@ -5631,6 +5632,12 @@
   </si>
   <si>
     <t>4b6f3fa4-10da-491a-9db5-d260361d8963.pdf + Soberanos(1).pdf</t>
+  </si>
+  <si>
+    <t>AO29</t>
+  </si>
+  <si>
+    <t>1226M</t>
   </si>
 </sst>
 </file>
@@ -5643,7 +5650,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%;[Red]\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5654,6 +5661,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -5681,7 +5695,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -5707,6 +5721,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5829,6 +5846,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>899160</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A6920C3-9D63-2C96-76AE-509BACFBA003}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5853,8 +5924,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaUniverso" displayName="TablaUniverso" ref="A1:R234" totalsRowShown="0">
-  <autoFilter ref="A1:R234" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaUniverso" displayName="TablaUniverso" ref="A1:R235" totalsRowShown="0">
+  <autoFilter ref="A1:R235" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Ticker"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Ley"/>
@@ -56773,7 +56844,45 @@
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="O235" s="7"/>
+      <c r="A235" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B235" t="s">
+        <v>516</v>
+      </c>
+      <c r="C235" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E235" s="11">
+        <v>46220</v>
+      </c>
+      <c r="F235" s="11">
+        <v>47422</v>
+      </c>
+      <c r="G235" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H235" t="s">
+        <v>1700</v>
+      </c>
+      <c r="J235">
+        <v>6</v>
+      </c>
+      <c r="K235">
+        <v>100</v>
+      </c>
+      <c r="M235" t="s">
+        <v>1058</v>
+      </c>
+      <c r="N235" s="11">
+        <v>46673</v>
+      </c>
+      <c r="O235" s="7" t="s">
+        <v>1701</v>
+      </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="O236" s="7"/>

--- a/cashflows_ON_USD_ley_ARG_NY_universo_solo_USD_2.xlsx
+++ b/cashflows_ON_USD_ley_ARG_NY_universo_solo_USD_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa-my.sharepoint.com/personal/mreverter_balanz_com/Documents/Escritorio/Info Solicitada/Cashflows net v2 - TEST LOCAL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_56DB888BAD2EA0C966F93D7708BFF57760A3A3CB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C5B73E-28F7-4280-8C13-5DB97C497673}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_56DB888BAD2EA0C966F93D7708BFF57760A3A3CB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD6BFFA1-85EA-43D4-8E1F-2F5F70F7A141}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflows" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8957" uniqueCount="1864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8973" uniqueCount="1865">
   <si>
     <t>Ticker</t>
   </si>
@@ -5638,6 +5638,9 @@
   </si>
   <si>
     <t>1226M</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA DE GAS DEL SUR S.A</t>
   </si>
 </sst>
 </file>
@@ -5900,6 +5903,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>899160</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4BA2879-DF01-F026-14B9-65F24E2C899D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5924,8 +5981,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaUniverso" displayName="TablaUniverso" ref="A1:R235" totalsRowShown="0">
-  <autoFilter ref="A1:R235" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaUniverso" displayName="TablaUniverso" ref="A1:R237" totalsRowShown="0">
+  <autoFilter ref="A1:R237" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Ticker"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Ley"/>
@@ -43737,7 +43794,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
@@ -56885,10 +56942,92 @@
       </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="O236" s="7"/>
+      <c r="A236" t="s">
+        <v>44</v>
+      </c>
+      <c r="B236" t="s">
+        <v>45</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E236" s="11">
+        <v>46203</v>
+      </c>
+      <c r="F236" s="11">
+        <v>50313</v>
+      </c>
+      <c r="G236" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H236" t="s">
+        <v>1700</v>
+      </c>
+      <c r="J236">
+        <v>7.55</v>
+      </c>
+      <c r="K236">
+        <v>100</v>
+      </c>
+      <c r="L236">
+        <v>2</v>
+      </c>
+      <c r="M236" t="s">
+        <v>1056</v>
+      </c>
+      <c r="N236" s="11">
+        <v>49582</v>
+      </c>
+      <c r="O236" s="7" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="O237" s="7"/>
+      <c r="A237" t="s">
+        <v>234</v>
+      </c>
+      <c r="B237" t="s">
+        <v>45</v>
+      </c>
+      <c r="C237" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E237" s="11">
+        <v>45981</v>
+      </c>
+      <c r="F237" s="11">
+        <v>49633</v>
+      </c>
+      <c r="G237" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H237" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J237">
+        <v>7.75</v>
+      </c>
+      <c r="K237">
+        <v>100</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
+      </c>
+      <c r="M237" t="s">
+        <v>1077</v>
+      </c>
+      <c r="N237" s="11">
+        <v>49633</v>
+      </c>
+      <c r="O237" s="7" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="O238" s="7"/>
